--- a/02_加值成品/九上/九上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-3 加速度　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上1-3 加速度　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>單位時間速度的變化是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>加速度</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>等加速度運動</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>加速</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>變化率</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>速度增加是加速還減速？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>減速</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>等加速度運動</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>等速或靜止</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>加速</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>增快</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>速度減少是加速還減速？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>減速</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>等速或靜止</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>等加速度運動</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>變慢</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>加速度是純量還向量？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>等加速度</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>速度值最高處</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>有方向</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>等速運動加速度是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>零</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>減速</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>加速度</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>等速或靜止</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>速度不變</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>速度均勻改變的運動是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>加速</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>速度值最高處</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>等加速度運動</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>均勻</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>速度-時間圖斜率代表？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>加速</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>等加速度</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>加速度</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>斜率</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>自由落體是哪種運動？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>等速或靜止</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>斜直線</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>等加速度</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>加速度的單位是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>m/s²</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>均勻增加(等加速)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>減速</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>單位</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>速度變快時加速度方向與運動方向？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>加速</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>等加速度</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>加速</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-3 加速度　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上1-3 加速度　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>v-t圖水平線表示？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>−4 m/s²</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>均勻增加(等加速)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>約9.8 m/s²</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>等速(加速度0)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>平</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>v-t圖向上斜線表示？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>減速</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>加速</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>加速度</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>速度增</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>v-t圖向下斜線表示？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>等速或靜止</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>等加速度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>減速</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>速度減</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>速度3秒由0增到6m/s,加速度？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>均勻增加(等加速)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2 m/s²</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>速度在改變即有加速度(負值)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>等加速度運動</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>6/3</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>煞車時加速度方向與速度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>相反</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>加速度</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>負</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>加速度為零代表？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>加速</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>等速或靜止</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>速度不變但方向變有加速度嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>減速</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>等加速度</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>向量變</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>等加速度v-t圖是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>斜直線</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>加速</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>速度值最高處</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>均勻</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>速度2秒由0到10m/s加速度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>等加速度</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>加速度越大速度變化越快</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>5 m/s²</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>10/2</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>汽車煞車變慢時加速度為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>負(與運動反向)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>−2 m/s²</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>等速(加速度0)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>速度在改變即有加速度(負值)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>減速</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-3 加速度　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上1-3 加速度　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>速度4秒內由10m/s減到2m/s,加速度？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>加速度越大速度變化越快</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>−2 m/s²</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>負(與運動反向)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>速度方向不斷改變</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>(2−10)/4</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何說減速也有加速度？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>加速度越大速度變化越快</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>負(與運動反向)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>速度在改變即有加速度(負值)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>均勻增加(等加速)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>v-t圖斜率越大代表？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>負(與運動反向)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>均勻增加(等加速)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>加速度越大速度變化越快</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>速度在改變即有加速度(負值)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>斜率</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>等速圓周運動速率不變為何有加速度？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>加速度越大速度變化越快</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>速度方向不斷改變</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不一定(如拋最高點)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>約9.8 m/s²</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>由v-t圖如何看出物體何時最快？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>速度值最高處</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>讀圖</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>自由落體速度如何隨時間？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>均勻增加(等加速)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>每秒速度增加2m/s</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>等速(加速度0)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>−2 m/s²</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>重力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>加速度2m/s²意義是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>均勻增加(等加速)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>負(與運動反向)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>−2 m/s²</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>每秒速度增加2m/s</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>速度為零時加速度一定為零嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>不一定(如拋最高點)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>速度在改變即有加速度(負值)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>−2 m/s²</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>等速(加速度0)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>瞬間</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>速度5秒由20減到0m/s加速度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>速度在改變即有加速度(負值)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>−4 m/s²</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>不一定(如拋最高點)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>速度方向不斷改變</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>(0−20)/5</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>自由落體加速度大約為多少？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>約9.8 m/s²</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不一定(如拋最高點)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>負(與運動反向)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>等速(加速度0)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>重力加速度</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>變化率</t>
+          <t>變化率：加速度是描述速度每單位時間改變了多少的量</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>增快</t>
+          <t>增快：只要速度數值變大,就代表物體正在加速</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>變慢</t>
+          <t>變慢：速度數值變小,代表物體正在減慢,也就是減速</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>有方向</t>
+          <t>有方向：加速度除了大小,還帶有方向,所以是向量</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>速度不變</t>
+          <t>速度不變：速度一直保持相同,代表沒有變化,加速度就是零</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>均勻</t>
+          <t>均勻：每一秒速度增加或減少的量都相同,叫做等加速度運動</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>斜率</t>
+          <t>斜率：速度對時間畫的圖,線段傾斜的程度就代表加速度大小</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>重力：物體只受重力自由下落,速度每秒均勻增加,屬於等加速度運動</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：加速度是速度隨時間的變化率,速度單位是m/s、時間單位是s,兩者相除就是m/s²</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>加速</t>
+          <t>加速：物體加速時,加速度的方向和運動方向一致,才會讓速度越來越快</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>平：圖形是水平線代表速度一直不變,加速度等於零</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>速度增</t>
+          <t>速度增：線段往上斜,表示速度隨時間持續增加,也就是在加速</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>速度減</t>
+          <t>速度減：線段往下斜,表示速度隨時間持續減少,也就是在減速</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>6/3</t>
+          <t>6/3：速度變化6公尺每秒除以時間3秒,等於每秒加速2公尺每秒</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>負</t>
+          <t>負：煞車讓速度變小,加速度方向和原本前進方向相反,是負值</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>不變：加速度為零表示速度完全沒有在改變,可能等速也可能靜止</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>向量變</t>
+          <t>向量變：即使快慢一樣,方向改變了速度這個向量整體也變了,所以有加速度</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>均勻</t>
+          <t>均勻：每段時間速度增減量都相同,畫出來會是一條傾斜的直線</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>10/2：加速度=速度變化量÷時間,10公尺/秒的變化除以2秒等於5m/s²</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>減速</t>
+          <t>減速：速度變小時,加速度方向和運動方向相反,習慣上稱為負加速度或減速度</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>(2−10)/4</t>
+          <t>(2−10)/4：末速2減初速10得到負8,再除以時間4秒,等於每秒負2公尺每秒</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：只要速度數值在改變,不管變快變慢,都算有加速度,只是方向相反</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>斜率</t>
+          <t>斜率：線段越陡,代表同樣時間內速度變化量越多,加速度就越大</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：速度是向量,雖然快慢不變,但繞圈時方向一直在變,所以有加速度</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>讀圖</t>
+          <t>讀圖：在速度時間圖上,曲線離時間軸最遠、數值最大的那一點就是最快</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>重力：只受重力作用下落,重力大小固定不變,所以速度會均勻地越來越快</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>定義</t>
+          <t>定義：這個數字代表每經過一秒,速度就會多增加2公尺每秒</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>瞬間</t>
+          <t>瞬間：像往上拋的球到最高點瞬間速度為零,但重力仍在作用,加速度不為零</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>(0−20)/5</t>
+          <t>(0−20)/5：加速度=(末速度−初速度)÷時間,(0−20)除以5等於−4m/s²,負號代表方向與原運動方向相反</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>重力加速度</t>
+          <t>重力加速度：物體只受重力自由落下時,加速度固定約為9.8m/s²,這就是重力加速度</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-3_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>等加速度運動</t>
+          <t>相反</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>加速</t>
+          <t>等速或靜止</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
           <t>減速</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>等加速度運動</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>減速</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>向量</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>加速</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>速度值最高處</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>零</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>加速</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>等加速度</t>
+          <t>等速或靜止</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>等速或靜止</t>
+          <t>向量</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>斜直線</t>
+          <t>有</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>加速</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>均勻增加(等加速)</t>
+          <t>斜直線</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>減速</t>
+          <t>等速或靜止</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>減速</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>零</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>加速度</t>
+          <t>等速或靜止</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>均勻增加(等加速)</t>
+          <t>5 m/s²</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>速度在改變即有加速度(負值)</t>
+          <t>等速(加速度0)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>等加速度運動</t>
+          <t>等速或靜止</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>等加速度</t>
+          <t>速度值最高處</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>加速度越大速度變化越快</t>
+          <t>−4 m/s²</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>零</t>
+          <t>等加速度運動</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
